--- a/docs/05_etc/Schedule.xlsx
+++ b/docs/05_etc/Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\WEBアプリ開発演習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0C99E2-DC3F-4BB8-AFC5-726AE41049B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0593FFD4-520D-4995-98A5-7C43BD6A6A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="70" yWindow="0" windowWidth="19220" windowHeight="10170" activeTab="1" xr2:uid="{47E68CCF-4E51-458B-8341-B277A73E4241}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{47E68CCF-4E51-458B-8341-B277A73E4241}"/>
   </bookViews>
   <sheets>
     <sheet name="予定" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="59">
   <si>
     <t>Mon</t>
   </si>
@@ -382,13 +382,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>遅れ</t>
-    <rPh sb="0" eb="1">
-      <t>オク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>メニューページ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -413,6 +406,20 @@
     </rPh>
     <rPh sb="6" eb="10">
       <t>コウゾウテイジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>進行中</t>
+    <rPh sb="0" eb="3">
+      <t>シンコウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遅延</t>
+    <rPh sb="0" eb="2">
+      <t>チエン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -450,7 +457,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -483,13 +490,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -565,13 +578,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1430,8 +1443,8 @@
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
-      <c r="W7" s="10" t="s">
-        <v>53</v>
+      <c r="W7" s="11" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.55000000000000004">
@@ -1460,6 +1473,9 @@
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
+      <c r="W8" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="6" t="s">
@@ -1549,7 +1565,7 @@
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F12" s="3"/>
@@ -1576,7 +1592,7 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F13" s="3"/>
@@ -1603,10 +1619,10 @@
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="9"/>
+      <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
@@ -1631,10 +1647,10 @@
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="11"/>
+      <c r="G15" s="9"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -1658,10 +1674,10 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="11"/>
+      <c r="G16" s="9"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
@@ -1685,8 +1701,8 @@
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11" t="s">
+      <c r="F17" s="9"/>
+      <c r="G17" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H17" s="4"/>
@@ -1713,7 +1729,7 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H18" s="4"/>
@@ -1748,8 +1764,8 @@
       <c r="L19" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="3"/>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
@@ -1777,7 +1793,7 @@
       <c r="N20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="O20" s="2"/>
+      <c r="O20" s="3"/>
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
@@ -1804,7 +1820,7 @@
       <c r="N21" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="O21" s="2"/>
+      <c r="O21" s="3"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
@@ -1829,7 +1845,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
-      <c r="O22" s="2" t="s">
+      <c r="O22" s="3" t="s">
         <v>47</v>
       </c>
       <c r="P22" s="2"/>
@@ -1856,7 +1872,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
-      <c r="O23" s="2" t="s">
+      <c r="O23" s="3" t="s">
         <v>47</v>
       </c>
       <c r="P23" s="2"/>
@@ -1884,7 +1900,7 @@
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-      <c r="P24" s="2" t="s">
+      <c r="P24" s="3" t="s">
         <v>49</v>
       </c>
       <c r="Q24" s="2"/>
@@ -1952,8 +1968,8 @@
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="12" t="s">
-        <v>54</v>
+      <c r="A27" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1982,17 +1998,17 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="C29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="C30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="C31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
